--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2153,6 +2153,810 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130087172</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>västanbäck Sv, västanbäck Sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468250</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6544834</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på redan tidigare känt fynd. Gran bredvid stor rotvälta tall.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130087132</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105881</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>468266</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6544839</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130085276</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>468154</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6544867</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på tall av tretåig hackspett I avvanm.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130086585</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>468332</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6544803</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sten.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130087073</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468387</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6544857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död tall.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130087065</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468396</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6544850</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död tall.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130086768</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468436</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6544822</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre födohack på död stående gran.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -2155,50 +2155,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130087172</v>
+        <v>130086585</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>56930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>västanbäck Sv, västanbäck Sv, Nrk</t>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468250</v>
+        <v>468332</v>
       </c>
       <c r="R15" t="n">
-        <v>6544834</v>
+        <v>6544803</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färskt ringhack på redan tidigare känt fynd. Gran bredvid stor rotvälta tall.</t>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,45 +2272,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130087132</v>
+        <v>130087073</v>
       </c>
       <c r="B16" t="n">
-        <v>105881</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468266</v>
+        <v>468387</v>
       </c>
       <c r="R16" t="n">
-        <v>6544839</v>
+        <v>6544857</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2357,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130085276</v>
+        <v>130086768</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,16 +2400,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2410,19 +2420,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>västanbäck sv, västanbäck sv, Nrk</t>
+          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468154</v>
+        <v>468436</v>
       </c>
       <c r="R17" t="n">
-        <v>6544867</v>
+        <v>6544822</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2454,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2474,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack med savflöde på tall av tretåig hackspett I avvanm.</t>
+          <t>Äldre födohack på död stående gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,50 +2506,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130086585</v>
+        <v>130087172</v>
       </c>
       <c r="B18" t="n">
-        <v>56930</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+          <t>västanbäck Sv, västanbäck Sv, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468332</v>
+        <v>468250</v>
       </c>
       <c r="R18" t="n">
-        <v>6544803</v>
+        <v>6544834</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2571,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,12 +2591,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Färskt ringhack på redan tidigare känt fynd. Gran bredvid stor rotvälta tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,50 +2623,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130087073</v>
+        <v>130087132</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>105881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468387</v>
+        <v>468266</v>
       </c>
       <c r="R19" t="n">
-        <v>6544857</v>
+        <v>6544839</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2688,7 +2697,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,12 +2707,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre födohack på stående död tall.</t>
+          <t>Ca 1 m2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,6 +2721,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2730,45 +2740,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130087065</v>
+        <v>130085276</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468396</v>
+        <v>468154</v>
       </c>
       <c r="R20" t="n">
-        <v>6544850</v>
+        <v>6544867</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2800,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,12 +2825,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På stående död tall.</t>
+          <t>Färska ringhack med savflöde på tall av tretåig hackspett I avvanm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,50 +2857,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130086768</v>
+        <v>130087065</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468436</v>
+        <v>468396</v>
       </c>
       <c r="R21" t="n">
-        <v>6544822</v>
+        <v>6544850</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2917,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2927,12 +2937,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre födohack på död stående gran.</t>
+          <t>På stående död tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -2626,7 +2626,7 @@
         <v>130087132</v>
       </c>
       <c r="B19" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>130086585</v>
       </c>
       <c r="B15" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>130087073</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>130086768</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>130087172</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130087132</v>
       </c>
       <c r="B19" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>130085276</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -2626,7 +2626,7 @@
         <v>130087132</v>
       </c>
       <c r="B19" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117026575</v>
+        <v>130086768</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,27 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>västanbäck sv, Nrk</t>
+          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468398</v>
+        <v>468436</v>
       </c>
       <c r="R2" t="n">
-        <v>6544908</v>
+        <v>6544822</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Alldeles färsk rinnande sav fr gran. (Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.)</t>
+          <t>Äldre födohack på död stående gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,32 +792,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117024672</v>
+        <v>130087073</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,27 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Nrk</t>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468169</v>
+        <v>468387</v>
       </c>
       <c r="R3" t="n">
-        <v>6544777</v>
+        <v>6544857</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,12 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,32 +909,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117025401</v>
+        <v>130087218</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,27 +938,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>västanbäck sv, Nrk</t>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468256</v>
+        <v>468207</v>
       </c>
       <c r="R4" t="n">
-        <v>6544844</v>
+        <v>6544805</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,17 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på 4 granar inne i avverkningsanmälan.</t>
+          <t>Äldre födohack på stående död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,32 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117024308</v>
+        <v>130087224</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,27 +1055,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>västanbäck Sv, Nrk</t>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468170</v>
+        <v>468160</v>
       </c>
       <c r="R5" t="n">
-        <v>6544780</v>
+        <v>6544800</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,17 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på ca 6-8 granar inne i avverkningsanmälan.</t>
+          <t>Äldre födohack på låga av gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,12 +1146,7 @@
         <v>117023940</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,15 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117024988</v>
+        <v>117024308</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,14 +1292,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>västanbäck sv, Nrk</t>
+          <t>västanbäck Sv, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468163</v>
+        <v>468170</v>
       </c>
       <c r="R7" t="n">
-        <v>6544778</v>
+        <v>6544780</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på ca 6-8 granar inne i avverkningsanmlan.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på ca 6-8 granar inne i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,12 +1366,7 @@
         <v>117024497</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,15 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117025202</v>
+        <v>117024672</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,14 +1507,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>västanbäck Sv, Nrk</t>
+          <t>Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468252</v>
+        <v>468169</v>
       </c>
       <c r="R9" t="n">
-        <v>6544837</v>
+        <v>6544777</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,11 +1547,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på 4 granar inne i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117026430</v>
+        <v>117024802</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468383</v>
+        <v>468163</v>
       </c>
       <c r="R10" t="n">
-        <v>6544905</v>
+        <v>6544780</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,11 +1652,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,15 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117026209</v>
+        <v>117024909</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468346</v>
+        <v>468166</v>
       </c>
       <c r="R11" t="n">
-        <v>6544881</v>
+        <v>6544772</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,7 +1761,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på ca 6-8 granar inne i avverkningsanmlan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,15 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117024909</v>
+        <v>117024988</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468166</v>
+        <v>468163</v>
       </c>
       <c r="R12" t="n">
-        <v>6544772</v>
+        <v>6544778</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,15 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117025459</v>
+        <v>117025202</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,14 +1937,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>västanbäck sv, Nrk</t>
+          <t>västanbäck Sv, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468250</v>
+        <v>468252</v>
       </c>
       <c r="R13" t="n">
-        <v>6544847</v>
+        <v>6544837</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2045,15 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117024802</v>
+        <v>117025401</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2041,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2093,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468163</v>
+        <v>468256</v>
       </c>
       <c r="R14" t="n">
-        <v>6544780</v>
+        <v>6544844</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,6 +2087,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre tretåhack och barkfläkningar på 4 granar inne i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,53 +2118,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130086585</v>
+        <v>117025459</v>
       </c>
       <c r="B15" t="n">
-        <v>57016</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+          <t>västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468332</v>
+        <v>468250</v>
       </c>
       <c r="R15" t="n">
-        <v>6544803</v>
+        <v>6544847</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2225,27 +2191,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på 4 granar inne i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130087073</v>
+        <v>117026077</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,16 +2239,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2301,24 +2257,27 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>västanbäck sv, västanbäck sv, Nrk</t>
+          <t>Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468387</v>
+        <v>468336</v>
       </c>
       <c r="R16" t="n">
-        <v>6544857</v>
+        <v>6544843</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,27 +2301,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre födohack på stående död tall.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130086768</v>
+        <v>117026209</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,16 +2349,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2418,24 +2367,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
+          <t>västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468436</v>
+        <v>468346</v>
       </c>
       <c r="R17" t="n">
-        <v>6544822</v>
+        <v>6544881</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2459,27 +2411,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre födohack på död stående gran.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130087172</v>
+        <v>117026430</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,24 +2477,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>västanbäck Sv, västanbäck Sv, Nrk</t>
+          <t>västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468250</v>
+        <v>468383</v>
       </c>
       <c r="R18" t="n">
-        <v>6544834</v>
+        <v>6544905</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2576,27 +2521,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färskt ringhack på redan tidigare känt fynd. Gran bredvid stor rotvälta tall.</t>
+          <t>Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,52 +2558,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130087132</v>
+        <v>117026575</v>
       </c>
       <c r="B19" t="n">
-        <v>105990</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>västanbäck sv, västanbäck sv, Nrk</t>
+          <t>västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468266</v>
+        <v>468398</v>
       </c>
       <c r="R19" t="n">
-        <v>6544839</v>
+        <v>6544908</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2692,27 +2631,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 1 m2</t>
+          <t>Alldeles färsk rinnande sav fr gran. (Färska och äldre tretåhack och barkfläkningar på upp emot 6 granar inne i avverkningsanmälan längs med gränsen mot hygget.)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,7 +2650,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2743,7 +2671,7 @@
         <v>130085276</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2857,45 +2785,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130087065</v>
+        <v>130086955</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>västanbäck sv, västanbäck sv, Nrk</t>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468396</v>
+        <v>468338</v>
       </c>
       <c r="R21" t="n">
-        <v>6544850</v>
+        <v>6544840</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2927,7 +2863,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,12 +2873,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stående död tall.</t>
+          <t>Färska ringhack med savflöde på gran med äldre ringhack med. Tidigare känt fynd. Fortsatt ringhackad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,6 +2902,698 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130087172</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>västanbäck Sv, västanbäck Sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>468250</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6544834</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på redan tidigare känt fynd. Gran bredvid stor rotvälta tall.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130086585</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>468332</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6544803</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sten.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130086675</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Visjöbäcken, Visjöbäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>468452</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6544780</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130694702</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>468095</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6544812</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med färska spårlöpor  av tjäder över vägen i nysnön.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130087065</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>468396</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6544850</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stående död tall.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130087132</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>västanbäck sv, västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>468266</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6544839</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 1 m2</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41520-2023 artfynd.xlsx
+++ b/artfynd/A 41520-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087218</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117023940</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024988</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117025202</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1881,6 +1936,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117025459</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1998,6 +2058,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085276</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2232,6 +2302,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130694702</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086768</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2466,6 +2546,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087073</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117025401</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117026077</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2796,6 +2891,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117026209</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117026430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3016,6 +3121,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117026575</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,6 +3246,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086955</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3253,6 +3368,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086585</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3365,6 +3485,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086675</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3477,6 +3602,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087065</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3594,8 +3724,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>